--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -159,6 +164,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -590,6 +598,30 @@
         <v>35.6</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026  16:35:34</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -605,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -688,6 +720,34 @@
         <v>4.8</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -622,6 +622,30 @@
         <v>40.4</v>
       </c>
       <c r="F3" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>18-Apr-2026  15:26:07</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -637,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -748,6 +772,34 @@
         <v>6.4</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>19-Apr-2026  15:26:11</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -661,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -800,6 +824,34 @@
         <v>6.4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>20-Apr-2026  16:50:40</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -685,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -852,6 +876,34 @@
         <v>6.4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>22-Apr-2026  04:50:31</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -709,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -904,6 +928,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -721,6 +721,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>22-Apr-2026  16:46:33</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -733,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -956,6 +980,34 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>23-Apr-2026  18:00:15</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -757,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1008,6 +1032,34 @@
         <v>7.6</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -769,6 +769,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026  16:42:09</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -781,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1060,6 +1084,34 @@
         <v>4.8</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -793,6 +793,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>25-Apr-2026  15:57:41</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -805,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1112,6 +1136,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -817,6 +817,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>26-Apr-2026  16:00:25</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -829,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1164,6 +1188,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -841,6 +841,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>27-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>27-Apr-2026  17:53:31</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -853,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1240,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>27-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -865,6 +865,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>27-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>28-Apr-2026  19:12:31</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -877,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1292,34 @@
         <v>12</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>27-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -889,6 +889,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>30-Apr-2026  16:10:46</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -901,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1320,6 +1344,34 @@
         <v>12</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -913,6 +913,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>01-May-2026  14:40:46</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -925,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1372,6 +1396,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -937,6 +937,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>04-May-2026  17:16:37</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -949,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1424,6 +1448,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>05-May-2026  16:30:51</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -973,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1476,6 +1500,34 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -985,6 +985,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>06-May-2026  16:25:35</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -997,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1528,6 +1552,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1009,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>07-May-2026  17:26:03</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1021,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1580,6 +1604,34 @@
         <v>10.8</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1033,6 +1033,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>08-May-2026  16:06:20</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1045,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1632,6 +1656,34 @@
         <v>10.8</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1057,6 +1057,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>11-May-2026  18:04:18</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1069,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1684,6 +1708,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1081,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>12-May-2026  18:20:45</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1093,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1736,6 +1760,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1105,6 +1105,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>13-May-2026  18:22:04</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1117,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1788,6 +1812,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1129,6 +1129,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>14-May-2026  17:27:34</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1141,7 +1165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1840,6 +1864,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1153,6 +1153,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>15-May-2026  17:12:58</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1165,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1892,6 +1916,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1177,6 +1177,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>18-May-2026  18:14:56</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1189,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1944,6 +1968,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1201,6 +1201,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>19-May-2026  13:55:13</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1213,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2020,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1225,6 +1225,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>20-May-2026  13:37:59</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1237,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2072,34 @@
         <v>6</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1249,6 +1249,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>21-May-2026  14:13:30</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1261,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2100,6 +2124,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1273,6 +1273,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>22-May-2026  13:29:37</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1285,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2176,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1297,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>25-May-2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>25-May-2026  13:58:53</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1309,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2204,6 +2228,34 @@
         <v>2</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>25-May-2026</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1321,6 +1321,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>26-May-2026  13:52:42</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1333,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2280,34 @@
         <v>6.8</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1345,6 +1345,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>27-May-2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>27-May-2026  14:25:29</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1357,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2308,6 +2332,34 @@
         <v>6</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>27-May-2026</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1369,6 +1369,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>27-May-2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>28-May-2026  14:35:44</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1381,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2360,6 +2384,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>27-May-2026</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1393,6 +1393,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>29-May-2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>29-May-2026  13:58:03</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1405,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2412,6 +2436,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>29-May-2026</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1417,6 +1417,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>01-Jun-2026  16:36:18</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1429,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2464,6 +2488,34 @@
         <v>4.8</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1441,6 +1441,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>02-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>02-Jun-2026  14:49:59</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1453,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2516,6 +2540,34 @@
         <v>3.21</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>02-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>5.62</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1465,6 +1465,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>03-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>03-Jun-2026  15:26:39</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1477,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2568,6 +2592,34 @@
         <v>5.62</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>03-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1489,6 +1489,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>04-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>04-Jun-2026  13:57:38</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1501,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2620,6 +2644,34 @@
         <v>1.61</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>04-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>5.22</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1513,6 +1513,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>05-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>05-Jun-2026  13:51:26</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1525,7 +1549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2672,6 +2696,34 @@
         <v>5.22</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>05-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1537,6 +1537,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026  03:45:47</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1549,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2724,6 +2748,34 @@
         <v>3.21</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1561,6 +1561,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026  04:28:20</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1573,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2776,6 +2800,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1585,6 +1585,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026  10:26:22</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1597,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2828,6 +2852,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1609,6 +1609,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026  10:46:59</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1621,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2880,6 +2904,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1633,6 +1633,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026  14:46:50</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1645,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2932,6 +2956,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1657,6 +1657,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026  05:45:10</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1669,7 +1693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2984,6 +3008,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026  06:01:59</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1693,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3036,6 +3060,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1705,6 +1705,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026  10:17:00</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1717,7 +1741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3088,6 +3112,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1729,6 +1729,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026  10:42:52</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1741,7 +1765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3140,6 +3164,34 @@
         <v>8.4</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1753,6 +1753,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026  13:43:17</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1765,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3192,6 +3216,34 @@
         <v>8.4</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1777,6 +1777,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>10-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>10-Jun-2026  14:21:12</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1789,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3244,6 +3268,34 @@
         <v>8.4</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>10-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1801,6 +1801,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026  05:34:10</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1813,7 +1837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3296,6 +3320,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1825,6 +1825,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026  14:34:18</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1837,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3348,6 +3372,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1849,6 +1849,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>12-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>12-Jun-2026  14:08:38</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1861,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3400,6 +3424,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>12-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1873,6 +1873,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026  16:15:09</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1885,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3452,6 +3476,34 @@
         <v>15.2</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H56" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1897,6 +1897,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>16-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>16-Jun-2026  15:51:02</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1909,7 +1933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3504,6 +3528,34 @@
         <v>10</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>16-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1921,6 +1921,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>17-Jun-2026  14:25:53</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1933,7 +1957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3556,6 +3580,34 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1945,6 +1945,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026  14:08:31</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1957,7 +1981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3608,6 +3632,34 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1969,6 +1969,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>19-Jun-2026  14:13:01</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1981,7 +2005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3660,6 +3684,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1993,6 +1993,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>22-Jun-2026  15:49:42</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2005,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3712,6 +3736,34 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H61" s="11" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2017,6 +2017,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026  13:42:58</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2029,7 +2053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3764,6 +3788,34 @@
         <v>6.4</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>24-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>24-Jun-2026  13:18:50</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3816,6 +3840,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>24-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2065,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026  13:14:14</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2077,7 +2101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3868,6 +3892,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H64" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2089,6 +2089,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-2026  13:09:09</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2101,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3920,6 +3944,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H65" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2113,6 +2113,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>29-Jun-2026  14:46:25</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2125,7 +2149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3972,6 +3996,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" s="11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2137,6 +2137,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>30-Jun-2026  13:08:46</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2149,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4024,6 +4048,34 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H67" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2161,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026  13:33:13</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2173,7 +2197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4076,6 +4100,34 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2185,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026  12:55:05</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2197,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4128,6 +4152,34 @@
         <v>2.41</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H69" s="11" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2209,6 +2209,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>03-Jul-2026  12:54:52</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2221,7 +2245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4180,6 +4204,34 @@
         <v>4.8</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2233,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026  14:22:40</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2245,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4232,6 +4256,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H71" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2257,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>07-Jul-2026  13:16:41</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2269,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4284,6 +4308,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2281,6 +2281,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>08-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>08-Jul-2026  12:18:17</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2293,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4336,6 +4360,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>08-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H73" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2305,6 +2305,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>09-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>09-Jul-2026  13:47:04</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2317,7 +2341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4388,6 +4412,34 @@
         <v>2</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>09-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2329,6 +2329,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>10-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>10-Jul-2026  13:09:41</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2341,7 +2365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4440,6 +4464,34 @@
         <v>9.199999999999999</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>10-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H75" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2353,6 +2353,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>13-Jul-2026  13:20:06</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2365,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4492,6 +4516,34 @@
         <v>6</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2377,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>14-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>14-Jul-2026  12:08:21</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2389,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4544,6 +4568,34 @@
         <v>4.4</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>14-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H77" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2401,6 +2401,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>15-Jul-2026  12:12:30</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2413,7 +2437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4596,6 +4620,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2425,6 +2425,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>16-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>16-Jul-2026  12:19:04</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2437,7 +2461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4648,6 +4672,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>16-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H79" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2449,6 +2449,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>17-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>17-Jul-2026  12:06:20</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2461,7 +2485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4700,6 +4724,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>17-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2473,6 +2473,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>20-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>20-Jul-2026  13:49:54</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2485,7 +2509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4752,6 +4776,34 @@
         <v>0.4</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>20-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2497,6 +2497,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>21-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>21-Jul-2026  12:22:36</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2509,7 +2533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4804,6 +4828,34 @@
         <v>6</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>21-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F82" s="9" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2521,6 +2521,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>22-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>22-Jul-2026  12:23:45</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2533,7 +2557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4856,6 +4880,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>22-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H83" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2545,6 +2545,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>23-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>23-Jul-2026  12:21:51</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2557,7 +2581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4908,6 +4932,34 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>23-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H84" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2569,6 +2569,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>24-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>24-Jul-2026  12:17:35</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2581,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4960,6 +4984,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>24-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H85" s="11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2593,6 +2593,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>27-Jul-2026  13:37:26</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2605,7 +2629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5012,6 +5036,34 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F86" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H86" s="11" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2617,6 +2617,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>28-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>28-Jul-2026  12:51:26</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2629,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5064,6 +5088,34 @@
         <v>6.4</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>28-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H87" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2641,6 +2641,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>29-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>29-Jul-2026  12:58:27</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D88" s="12" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2653,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5116,6 +5140,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>29-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F88" s="9" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H88" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2665,6 +2665,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>30-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>30-Jul-2026  12:27:19</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="D89" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2677,7 +2701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5168,6 +5192,34 @@
         <v>2</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>30-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H89" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2689,6 +2689,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>31-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31-Jul-2026  12:53:28</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D90" s="12" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2701,7 +2725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5220,6 +5244,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>31-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H90" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2713,6 +2713,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>03-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03-Aug-2026  13:38:41</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2725,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5272,6 +5296,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>03-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H91" s="11" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2737,6 +2737,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>04-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>04-Aug-2026  12:58:49</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2749,7 +2773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5324,6 +5348,34 @@
         <v>10.4</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>04-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H92" s="11" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2761,6 +2761,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>05-Aug-2026  12:50:08</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2773,7 +2797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5376,6 +5400,34 @@
         <v>11.2</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H93" s="11" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2785,6 +2785,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>06-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>06-Aug-2026  12:54:09</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2797,7 +2821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5428,6 +5452,34 @@
         <v>7.2</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>06-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F94" s="9" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H94" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2809,6 +2809,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>07-Aug-2026  11:42:57</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2821,7 +2845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5480,6 +5504,34 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H95" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2833,6 +2833,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>10-Aug-2026  11:44:14</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="D96" s="12" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2845,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5532,6 +5556,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="9" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2857,6 +2857,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>11-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>11-Aug-2026  11:40:48</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2869,7 +2893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5584,6 +5608,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>11-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H97" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2881,6 +2881,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>12-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>12-Aug-2026  11:42:52</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2893,7 +2917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5636,6 +5660,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>12-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F98" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H98" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2905,6 +2905,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>13-Aug-2026  11:42:39</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2917,7 +2941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5688,6 +5712,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H99" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EMA Breadth History" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="nifty 50_ema_breadth_history" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMA Breadth History" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nifty 50_ema_breadth_history" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EMA Breadth History'!$A$1:$F$1</definedName>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2929,6 +2929,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>14-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>14-Aug-2026  11:41:58</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D100" s="12" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2941,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5740,6 +5764,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>14-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H100" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2953,6 +2953,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>17-Aug-2026  11:21:15</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2965,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5792,6 +5816,34 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H101" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2977,6 +2977,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>18-Aug-2026  11:21:25</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D102" s="12" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2989,7 +3013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5844,6 +5868,34 @@
         <v>6</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H102" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3001,6 +3001,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>19-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>19-Aug-2026  11:21:16</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3013,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5896,6 +5920,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>19-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H103" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3025,6 +3025,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>20-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>20-Aug-2026  11:22:31</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3037,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5948,6 +5972,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>20-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="9" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H104" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3049,6 +3049,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>21-Aug-2026  11:21:57</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3061,7 +3085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6000,6 +6024,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H105" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3073,6 +3073,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>24-Aug-2026  11:23:17</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3085,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6052,6 +6076,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H106" s="11" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3097,6 +3097,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>25-Aug-2026  11:23:21</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3109,7 +3133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6104,6 +6128,34 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H107" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3121,6 +3121,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-2026  11:25:46</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3133,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6156,6 +6180,34 @@
         <v>3.2</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F108" s="9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H108" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3145,6 +3145,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>27-Aug-2026  20:54:04</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3157,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6208,6 +6232,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H109" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3169,6 +3169,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>28-Aug-2026  21:19:19</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3181,7 +3205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6260,6 +6284,34 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3193,6 +3193,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>31-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>31-Aug-2026  17:50:12</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3205,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6312,6 +6336,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>31-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H111" s="11" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3217,6 +3217,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>01-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>01-Sep-2026  15:23:05</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3229,7 +3253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6364,6 +6388,34 @@
         <v>3.6</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>01-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3241,6 +3241,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>02-Sep-2026  14:56:15</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3253,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6416,6 +6440,34 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H113" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3265,6 +3265,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>03-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>03-Sep-2026  14:51:36</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3277,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6468,6 +6492,34 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>03-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth_history.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3289,6 +3289,30 @@
         <v>250</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>04-Sep-2026  14:45:08</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3301,7 +3325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6520,6 +6544,34 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G115" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H115" s="11" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
